--- a/transcricoes_audios.xlsx
+++ b/transcricoes_audios.xlsx
@@ -575,7 +575,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Acesso a sistemas do FNDE (prestação de contas)</t>
+          <t>Acesso ao SIGECON (FNDE)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -583,11 +583,7 @@
           <t>Problema de acesso</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>"SIGECON" provavelmente = SiGPC (FNDE).</t>
-        </is>
-      </c>
+      <c r="H2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -611,7 +607,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Acesso a sistemas do FNDE (prestação de contas)</t>
+          <t>Acesso ao SIGECON (FNDE)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1041,7 +1037,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Acesso a sistemas do FNDE (prestação de contas)</t>
+          <t>Acesso ao SIGECON (FNDE)</t>
         </is>
       </c>
       <c r="B2" s="5">
